--- a/XLS-005 - Requirements Traceability Matrix - v0.2.xlsx
+++ b/XLS-005 - Requirements Traceability Matrix - v0.2.xlsx
@@ -491,10 +491,11 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>PMOC Software | Fase 1 | v0.2 DRAFT | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved | Status: aguardando segunda revisão formal da Services.NET | Estrutura criada na Fase 1; preenchimento completo ocorre a partir da Fase 2.</t>
-        </is>
-      </c>
-    </row>
+          <t>PMOC Software | Fase 1 | v0.2 — APPROVED | 22/09/2026 | Origem das alterações: Services.NET Phase 1 Audit — Approved; Services.NET segunda revisão formal da Fase 1 v0.2 | Status: APPROVED WITH OPEN ACTIONS — Fase 1 aprovada formalmente pela Services.NET em 22/09/2026; Fase 2 não iniciada | Estrutura criada na Fase 1; preenchimento completo ocorre a partir da Fase 2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="8">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -1685,10 +1686,11 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Cada requisito possui identificador único e imutável. Identificador de requisito substituído NUNCA é reaproveitado para conceito diferente. | v0.2 DRAFT</t>
-        </is>
-      </c>
-    </row>
+          <t>Cada requisito possui identificador único e imutável. Identificador de requisito substituído NUNCA é reaproveitado para conceito diferente. | v0.2 — APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="8">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -1874,10 +1876,11 @@
     <row r="2" ht="15" customHeight="1" s="8">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Requisito sem cadeia completa não atende à Definition of Done. O elo 'API' admite ausência justificada quando o comportamento for estritamente local da interface. | v0.2 DRAFT</t>
-        </is>
-      </c>
-    </row>
+          <t>Requisito sem cadeia completa não atende à Definition of Done. O elo 'API' admite ausência justificada quando o comportamento for estritamente local da interface. | v0.2 — APPROVED</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="8">
       <c r="A4" s="11" t="inlineStr">
         <is>
@@ -2066,6 +2069,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="8">
       <c r="A4" s="14" t="inlineStr">
         <is>
